--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488142_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488142_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0271</v>
+        <v>2.5621</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3086</v>
+        <v>2.8189</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2814</v>
+        <v>-0.2568</v>
       </c>
       <c r="G2" t="n">
         <v>1.3697</v>
@@ -610,13 +610,13 @@
         <v>1.297</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.1918</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.2901</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1229</v>
+        <v>-0.0982</v>
       </c>
       <c r="V2" t="n">
         <v>0.63</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8018</v>
+        <v>1.4105</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5463</v>
+        <v>2.4259</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-1.0154</v>
       </c>
       <c r="G3" t="n">
         <v>-0.4761</v>
@@ -688,13 +688,13 @@
         <v>2.0382</v>
       </c>
       <c r="S3" t="n">
-        <v>2.498</v>
+        <v>1.1068</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0519</v>
+        <v>0.9314</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4462</v>
+        <v>0.1753</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2583</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ AMESTOY</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.0702</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0915</v>
+        <v>0.9318</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0214</v>
+        <v>-1.002</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.8937</v>
+        <v>-1.5528</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8245</v>
+        <v>-0.8646</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0692</v>
+        <v>-0.6882</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.7829</v>
+        <v>3.033</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1514</v>
+        <v>1.6016</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6315</v>
+        <v>1.4314</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1108</v>
+        <v>-4.5858</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6731</v>
+        <v>-2.4663</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4377</v>
+        <v>-2.1196</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6676</v>
+        <v>1.297</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6676</v>
+        <v>3.3352</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2957</v>
+        <v>0.1856</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6156</v>
+        <v>-0.0631</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3198</v>
+        <v>0.2487</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>A. FERNANDEZ AMESTOY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0352</v>
+        <v>-0.8494</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2549</v>
+        <v>-0.0496</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7804</v>
+        <v>-0.7998</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5528</v>
+        <v>-2.8937</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8646</v>
+        <v>-1.8245</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6882</v>
+        <v>-1.0692</v>
       </c>
       <c r="J7" t="n">
-        <v>3.033</v>
+        <v>-1.7829</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6016</v>
+        <v>-1.1514</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4314</v>
+        <v>-0.6315</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.5858</v>
+        <v>-1.1108</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.4663</v>
+        <v>-0.6731</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1196</v>
+        <v>-0.4377</v>
       </c>
       <c r="P7" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.3352</v>
+        <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7794</v>
+        <v>0.3762</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2497</v>
+        <v>0.4744</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4703</v>
+        <v>-0.0982</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3358</v>
+        <v>-2.0864</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.1347</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7547</v>
+        <v>-1.9517</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1448</v>
@@ -1078,13 +1078,13 @@
         <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1736</v>
+        <v>0.0759</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6566</v>
+        <v>-0.2101</v>
       </c>
       <c r="U8" t="n">
-        <v>0.483</v>
+        <v>0.286</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5733</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3472</v>
+        <v>-2.1453</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7239</v>
+        <v>-1.5713</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6233</v>
+        <v>-0.574</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3004</v>
@@ -1156,13 +1156,13 @@
         <v>1.8529</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1385</v>
+        <v>0.3404</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1144</v>
+        <v>0.2671</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0241</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>A. VICENTE FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1269</v>
+        <v>-2.9107</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2615</v>
+        <v>-4.1102</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8655</v>
+        <v>1.1994</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.2343</v>
+        <v>-1.4518</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5923</v>
+        <v>-0.206</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.642</v>
+        <v>-1.2458</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.757</v>
+        <v>-0.7934</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2286</v>
+        <v>0.4294</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5284</v>
+        <v>-1.2228</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4773</v>
+        <v>-0.6584</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3637</v>
+        <v>-0.6354</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1136</v>
+        <v>-0.023</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7793</v>
+        <v>-3.7057</v>
       </c>
       <c r="R10" t="n">
         <v>1.6676</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3308</v>
+        <v>0.5792</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0721</v>
+        <v>0.3889</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2586</v>
+        <v>0.1903</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. VICENTE FERNANDEZ</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.192</v>
+        <v>-3.4459</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3175</v>
+        <v>-2.4573</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1256</v>
+        <v>-0.9886</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4518</v>
+        <v>-4.2343</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.206</v>
+        <v>-2.5923</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2458</v>
+        <v>-1.642</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7934</v>
+        <v>-1.757</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4294</v>
+        <v>-1.2286</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2228</v>
+        <v>-0.5284</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6584</v>
+        <v>-2.4773</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6354</v>
+        <v>-1.3637</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.023</v>
+        <v>-1.1136</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.7057</v>
+        <v>-2.7793</v>
       </c>
       <c r="R11" t="n">
         <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>0.298</v>
+        <v>0.0118</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1816</v>
+        <v>-0.1237</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1164</v>
+        <v>0.1355</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6236</v>
+        <v>-3.4518</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8871</v>
+        <v>-2.7892</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7365</v>
+        <v>-0.6626</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4554</v>
@@ -1390,13 +1390,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2243</v>
+        <v>-0.0525</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1977</v>
+        <v>-0.0998</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0266</v>
+        <v>0.0473</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3144</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7308</v>
+        <v>-3.5344</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0263</v>
+        <v>-2.9284</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7045</v>
+        <v>-0.606</v>
       </c>
       <c r="G13" t="n">
         <v>-3.9693</v>
@@ -1468,13 +1468,13 @@
         <v>0.7411</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5026</v>
+        <v>-0.3062</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4377</v>
+        <v>-0.3398</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0649</v>
+        <v>0.0336</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.4009</v>
+        <v>-5.2483</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.229</v>
+        <v>-3.0763</v>
       </c>
       <c r="F14" t="n">
         <v>-2.172</v>
@@ -1546,10 +1546,10 @@
         <v>1.297</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2736</v>
+        <v>-0.1209</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4713</v>
+        <v>-0.3186</v>
       </c>
       <c r="U14" t="n">
         <v>0.1977</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.1982</v>
+        <v>-5.7747</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.4192</v>
+        <v>-3.2666</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.779</v>
+        <v>-2.5081</v>
       </c>
       <c r="G15" t="n">
         <v>-2.415</v>
@@ -1624,13 +1624,13 @@
         <v>2.594</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5979</v>
+        <v>-0.1744</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3109</v>
+        <v>-0.1582</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.287</v>
+        <v>-0.0162</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8883</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-25.4474</v>
+        <v>-24.9003</v>
       </c>
       <c r="E16" t="n">
-        <v>-14.1099</v>
+        <v>-13.5628</v>
       </c>
       <c r="F16" t="n">
         <v>-11.3376</v>
@@ -1702,13 +1702,13 @@
         <v>20.3817</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6664</v>
+        <v>2.2137</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4914</v>
+        <v>1.0386</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1751</v>
+        <v>1.1752</v>
       </c>
       <c r="V16" t="n">
         <v>-4.4038</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CASTILLO ORTEGA</t>
+          <t>R. GUERRA ZAYAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>9.5181</v>
+        <v>9.322100000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>7.6041</v>
+        <v>7.7622</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9141</v>
+        <v>1.5599</v>
       </c>
       <c r="G17" t="n">
-        <v>7.1799</v>
+        <v>6.9618</v>
       </c>
       <c r="H17" t="n">
-        <v>6.146</v>
+        <v>1.4937</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0339</v>
+        <v>5.4681</v>
       </c>
       <c r="J17" t="n">
-        <v>6.9147</v>
+        <v>7.1963</v>
       </c>
       <c r="K17" t="n">
-        <v>6.1576</v>
+        <v>2.074</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7572</v>
+        <v>5.1223</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2652</v>
+        <v>-0.2345</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0115</v>
+        <v>-0.5803</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2767</v>
+        <v>0.3457</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7411</v>
+        <v>0.7411</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9646</v>
+        <v>-1.1117</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2234</v>
+        <v>1.8529</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5072</v>
+        <v>-0.2686</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1379</v>
+        <v>-0.2101</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3693</v>
+        <v>-0.0585</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5722</v>
+        <v>1.8877</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5161</v>
+        <v>1.8877</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GUERRA ZAYAS</t>
+          <t>A. CASTILLO ORTEGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>8.5953</v>
+        <v>8.553800000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>7.3705</v>
+        <v>6.6248</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2249</v>
+        <v>1.929</v>
       </c>
       <c r="G18" t="n">
-        <v>6.9618</v>
+        <v>7.1799</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4937</v>
+        <v>6.146</v>
       </c>
       <c r="I18" t="n">
-        <v>5.4681</v>
+        <v>1.0339</v>
       </c>
       <c r="J18" t="n">
-        <v>7.1963</v>
+        <v>6.9147</v>
       </c>
       <c r="K18" t="n">
-        <v>2.074</v>
+        <v>6.1576</v>
       </c>
       <c r="L18" t="n">
-        <v>5.1223</v>
+        <v>0.7572</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2345</v>
+        <v>0.2652</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5803</v>
+        <v>-0.0115</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3457</v>
+        <v>0.2767</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7411</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1117</v>
+        <v>-2.9646</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8529</v>
+        <v>2.2234</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9953</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6019</v>
+        <v>0.1586</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3935</v>
+        <v>0.3842</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8877</v>
+        <v>1.5722</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8877</v>
+        <v>2.5161</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.479</v>
+        <v>2.5277</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7261</v>
+        <v>0.824</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7529</v>
+        <v>1.7037</v>
       </c>
       <c r="G19" t="n">
         <v>0.8544</v>
@@ -1936,13 +1936,13 @@
         <v>1.6676</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1721</v>
+        <v>-0.1234</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0467</v>
+        <v>-0.0025</v>
       </c>
       <c r="V19" t="n">
         <v>0.3144</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8113</v>
+        <v>1.9402</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3922</v>
+        <v>-0.0985</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2035</v>
+        <v>2.0386</v>
       </c>
       <c r="G20" t="n">
         <v>2.9208</v>
@@ -2014,13 +2014,13 @@
         <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2567</v>
+        <v>-0.1278</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4924</v>
+        <v>-0.1986</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2357</v>
+        <v>0.0709</v>
       </c>
       <c r="V20" t="n">
         <v>0.6294</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CARBU RODRIGUEZ</t>
+          <t>U. CHAGOYEN SALGUERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5976</v>
+        <v>1.8668</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5746</v>
+        <v>0.9644</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0229</v>
+        <v>0.9024</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6022</v>
+        <v>1.6458</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.152</v>
+        <v>1.1235</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7543</v>
+        <v>0.5223</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5236</v>
+        <v>1.0306</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3992</v>
+        <v>1.0306</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1244</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0786</v>
+        <v>0.6152</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5513</v>
+        <v>0.0929</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6299</v>
+        <v>0.5223</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6248</v>
+        <v>0.221</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9774</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3527</v>
+        <v>0.2873</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. RUESGA MORALES</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5463</v>
+        <v>1.6241</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.225</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7712</v>
+        <v>2.4231</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1226</v>
+        <v>1.5169</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5393</v>
+        <v>0.719</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8197</v>
+        <v>1.3073</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9488</v>
+        <v>1.1722</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8709</v>
+        <v>0.1351</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3029</v>
+        <v>0.2096</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3656</v>
+        <v>-0.3743</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6685</v>
+        <v>0.5839</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.5205</v>
+        <v>0.1853</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.5586</v>
+        <v>-1.8529</v>
       </c>
       <c r="R22" t="n">
         <v>2.0382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7409</v>
+        <v>-0.078</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0037</v>
+        <v>-0.2534</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7446</v>
+        <v>0.1753</v>
       </c>
       <c r="V22" t="n">
-        <v>2.2033</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>U. CHAGOYEN SALGUERO</t>
+          <t>F. RUESGA MORALES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.466</v>
+        <v>1.4386</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8665</v>
+        <v>-1.3229</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5995</v>
+        <v>2.7615</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6458</v>
+        <v>2.1226</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1235</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5223</v>
+        <v>1.5393</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0306</v>
+        <v>1.8197</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0306</v>
+        <v>0.9488</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.8709</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6152</v>
+        <v>0.3029</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0929</v>
+        <v>-0.3656</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5223</v>
+        <v>0.6685</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-3.5205</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-5.5586</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1798</v>
+        <v>0.6333</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1641</v>
+        <v>-0.1016</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0157</v>
+        <v>0.7349</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2.2033</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>J. CARBU RODRIGUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8476</v>
+        <v>1.1171</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0927</v>
+        <v>-0.2088</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9403</v>
+        <v>1.3258</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5169</v>
+        <v>0.6022</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7979000000000001</v>
+        <v>-0.152</v>
       </c>
       <c r="I24" t="n">
-        <v>0.719</v>
+        <v>0.7543</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3073</v>
+        <v>0.5236</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1722</v>
+        <v>0.3992</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1351</v>
+        <v>0.1244</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2096</v>
+        <v>0.0786</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3743</v>
+        <v>-0.5513</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5839</v>
+        <v>0.6299</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1853</v>
+        <v>0.3706</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0382</v>
+        <v>1.297</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8546</v>
+        <v>0.1443</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5471</v>
+        <v>0.194</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3074</v>
+        <v>-0.0497</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3882</v>
+        <v>0.1903</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.6462</v>
+        <v>-2.1565</v>
       </c>
       <c r="F26" t="n">
-        <v>2.258</v>
+        <v>2.3468</v>
       </c>
       <c r="G26" t="n">
         <v>-0.3777</v>
@@ -2482,13 +2482,13 @@
         <v>2.4087</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.381</v>
+        <v>0.1974</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6566</v>
+        <v>-0.1669</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2755</v>
+        <v>0.3643</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.585</v>
+        <v>0.0363</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.3802</v>
+        <v>-1.0865</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7952</v>
+        <v>1.1227</v>
       </c>
       <c r="G27" t="n">
         <v>0.8768</v>
@@ -2560,13 +2560,13 @@
         <v>1.4823</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.2204</v>
+        <v>-0.5991</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4924</v>
+        <v>-0.1986</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.728</v>
+        <v>-0.4004</v>
       </c>
       <c r="V27" t="n">
         <v>0.3144</v>
@@ -2581,7 +2581,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>A. CALLE GOMEZ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,73 +2593,73 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8643</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6873</v>
+        <v>-1.2793</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.5516</v>
+        <v>0.4572</v>
       </c>
       <c r="G28" t="n">
-        <v>1.7512</v>
+        <v>-1.1874</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0784</v>
+        <v>-1.1397</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6728</v>
+        <v>-0.0476</v>
       </c>
       <c r="J28" t="n">
-        <v>2.508</v>
+        <v>-1.1584</v>
       </c>
       <c r="K28" t="n">
-        <v>1.1809</v>
+        <v>-0.5884</v>
       </c>
       <c r="L28" t="n">
-        <v>1.3271</v>
+        <v>-0.5699</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.7568</v>
+        <v>-0.029</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.1026</v>
+        <v>-0.5513</v>
       </c>
       <c r="O28" t="n">
-        <v>0.3457</v>
+        <v>0.5223</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.0977</v>
+        <v>-0.0053</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1057</v>
+        <v>-0.1209</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.2035</v>
+        <v>0.1156</v>
       </c>
       <c r="V28" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A. CALLE GOMEZ</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2671,67 +2671,67 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.1983</v>
+        <v>-1.0109</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.3772</v>
+        <v>1.4914</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1789</v>
+        <v>-2.5023</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.1874</v>
+        <v>1.7512</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.1397</v>
+        <v>0.0784</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0476</v>
+        <v>1.6728</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.1584</v>
+        <v>2.508</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.5884</v>
+        <v>1.1809</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.5699</v>
+        <v>1.3271</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.029</v>
+        <v>-0.7568</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.5513</v>
+        <v>-1.1026</v>
       </c>
       <c r="O29" t="n">
-        <v>0.5223</v>
+        <v>0.3457</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.3815</v>
+        <v>-0.2444</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.2189</v>
+        <v>-0.0901</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1627</v>
+        <v>-0.1542</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="30">
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>25.4475</v>
+        <v>27.4061</v>
       </c>
       <c r="E30" t="n">
-        <v>11.3377</v>
+        <v>11.3375</v>
       </c>
       <c r="F30" t="n">
-        <v>14.1098</v>
+        <v>16.0684</v>
       </c>
       <c r="G30" t="n">
         <v>25.4894</v>
@@ -2782,7 +2782,7 @@
         <v>-2.8143</v>
       </c>
       <c r="O30" t="n">
-        <v>4.532999999999999</v>
+        <v>4.533</v>
       </c>
       <c r="P30" t="n">
         <v>-2.7793</v>
@@ -2794,13 +2794,13 @@
         <v>17.6023</v>
       </c>
       <c r="S30" t="n">
-        <v>-1.6662</v>
+        <v>0.2922000000000001</v>
       </c>
       <c r="T30" t="n">
-        <v>-1.175</v>
+        <v>-1.1747</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.4917</v>
+        <v>1.4672</v>
       </c>
       <c r="V30" t="n">
         <v>4.403700000000001</v>
